--- a/Forecasts/Forecast-27062026-12Z.xlsx
+++ b/Forecasts/Forecast-27062026-12Z.xlsx
@@ -662,7 +662,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 27/06/2026 22:22</t>
+          <t>Généré le : 28/06/2026 22:22</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 27/06/2026 22:22</t>
+          <t>Généré le : 28/06/2026 22:22</t>
         </is>
       </c>
     </row>

--- a/Forecasts/Forecast-27062026-12Z.xlsx
+++ b/Forecasts/Forecast-27062026-12Z.xlsx
@@ -662,7 +662,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 28/06/2026 22:22</t>
+          <t>Généré le : 29/06/2026 06:01</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 28/06/2026 22:22</t>
+          <t>Généré le : 29/06/2026 06:01</t>
         </is>
       </c>
     </row>
